--- a/outputs/evaluation/requirement/design/v2/gemini-3-5-flash-lite/CF_M01/first/CF_M01_req_eval.xlsx
+++ b/outputs/evaluation/requirement/design/v2/gemini-3-5-flash-lite/CF_M01/first/CF_M01_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.9667</v>
       </c>
       <c r="D13" t="n">
+        <v>0.9831</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.978</v>
       </c>
     </row>
@@ -755,10 +763,6 @@
           <t>The system shall allow listing the different actions performed on the different entities of the platform.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>FR</t>
@@ -773,10 +777,6 @@
 platform entities</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -807,10 +807,6 @@
           <t>The system shall allow listing the different connections of the system's players.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>FR</t>
@@ -824,10 +820,6 @@
           <t>Be able to list the different player connections in the system</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -858,10 +850,6 @@
           <t>The system shall allow listing the different playlogs of the system.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>FR</t>
@@ -875,10 +863,6 @@
           <t>Be able to list the different playlogs of the system</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -909,10 +893,6 @@
           <t>The system shall save the connections of the players.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>FR</t>
@@ -926,10 +906,6 @@
           <t>System saves player connections</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -960,14 +936,11 @@
           <t>Users without permission cannot access data for which they do not have permission.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>R_26</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -981,14 +954,11 @@
           <t>Unauthorized users cannot access data they do not own.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>CF_M01_R023</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1019,14 +989,11 @@
           <t>All details of the playlog must be viewable.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>R_09</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1040,14 +1007,11 @@
           <t>You must be able to see all the details of the playlog.</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>CF_M01_R09</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1078,10 +1042,6 @@
           <t>The system shall save the playlogs of the players.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1095,10 +1055,6 @@
           <t>System saves the players' playlogs</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1129,14 +1085,11 @@
           <t>Each action has a date, client, user, and player assigned.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>R_06</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1150,14 +1103,11 @@
           <t>Each action has an assigned date, client and player.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>CF_M01_R06</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1193,9 +1143,6 @@
           <t>C_06</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1220,8 +1167,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1252,10 +1197,6 @@
           <t>The system shall save the actions performed on the platform.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1269,10 +1210,6 @@
           <t>System saves the actions carried out on the platform</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1303,14 +1240,11 @@
           <t>The system scales automatically as data increases.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>R_24</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1324,14 +1258,11 @@
           <t>The system scales automatically as they go increasing the data.</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>CF_M01_R24</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1367,9 +1298,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1393,8 +1321,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1425,14 +1351,11 @@
           <t>Users can only view the confidential data of their own user and no one else's.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>R_28</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1446,14 +1369,11 @@
           <t>Users can only view their confidential data user and no one else.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>CF_M01_R025</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1484,14 +1404,11 @@
           <t>The platform scales dynamically with changes in simultaneous connections.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>R_22</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1505,14 +1422,11 @@
           <t>The platform scales dynamically with changes in connections simultaneous.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CF_M01_R22</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1543,14 +1457,11 @@
           <t>The actions that the user can see will depend on the permissions they have.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1564,14 +1475,11 @@
           <t>The actions that the user will be able to see will depend on the permissions it has</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>CF_M01_R015</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1602,14 +1510,11 @@
           <t>The connection state can only be connected or not connected.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>R_03</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1623,14 +1528,11 @@
           <t>The connection status can only be connected or not connected.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>CF_M01_R03</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1661,14 +1563,11 @@
           <t>The playlogs that the user can see will depend on the permissions they have.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>R_09</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1682,14 +1581,11 @@
           <t>The playlogs that the user will be able to see will depend on the permissions it has</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>CF_M01_R09</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1720,14 +1616,11 @@
           <t>Each connection has a date, client, and player assigned.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>R_03</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1741,14 +1634,11 @@
           <t>Each connection has an assigned date, client, player.</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>CF_M01_R03</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1779,14 +1669,11 @@
           <t>Any user must be able to access the platform at any time of the day, except during scheduled updates.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1800,14 +1687,11 @@
           <t>Any user must be able to access the platform during any time time of day. Except for scheduled updates.</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>CF_M01_R20</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1838,14 +1722,11 @@
           <t>The connections that the user can see will depend on the permissions they have.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1859,14 +1740,11 @@
           <t>The connections that the user will be able to see will depend on the permissions it has.</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>CF_M01_R12</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1897,14 +1775,11 @@
           <t>Each playlog has a date, client, and player assigned.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1918,14 +1793,11 @@
           <t>Each playlog has an assigned date, client, player.</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>CF_M01_R01</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1961,9 +1833,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1987,8 +1856,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2019,14 +1886,11 @@
           <t>All actions must be related to an entity of the platform.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2040,14 +1904,11 @@
           <t>All actions must be related to an entity the platform.</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>CF_M01_R015</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2078,14 +1939,11 @@
           <t>The system responds to any user action in less than 5 seconds.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>R_18</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2099,14 +1957,11 @@
           <t>The system responds to any user action in less than 5 seconds.</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>CF_M01_R018</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2137,14 +1992,11 @@
           <t>Connections can only have two states: connected or not connected.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2158,14 +2010,11 @@
           <t>Connections can only have two states: connected or not connected.</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>CF_M01_R12</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2201,9 +2050,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2228,8 +2074,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2265,9 +2109,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2291,8 +2132,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2323,14 +2162,11 @@
           <t>All actions are performed on an entity of the platform.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>R_06</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2344,14 +2180,11 @@
           <t>All actions are performed on an entity of the platform.</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>CF_M01_R06</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2387,9 +2220,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2413,8 +2243,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
